--- a/data/trans_orig/P1426-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1426-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2012</t>
+          <t>Población con diagnóstico de hipoacusia en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>673383</t>
+          <t>673400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686162</t>
+          <t>686155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>598178</t>
+          <t>598241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609321</t>
+          <t>609319</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1279220</t>
+          <t>1278785</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294406</t>
+          <t>1294399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18480</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671065</t>
+          <t>670327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680115</t>
+          <t>680055</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>697213</t>
+          <t>697975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707875</t>
+          <t>708533</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1372957</t>
+          <t>1373792</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1386906</t>
+          <t>1386987</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604137</t>
+          <t>604204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613582</t>
+          <t>613589</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601835</t>
+          <t>601123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612140</t>
+          <t>612124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1210242</t>
+          <t>1209498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1223739</t>
+          <t>1223656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>27343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>409808</t>
+          <t>410283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>423901</t>
+          <t>423969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>435059</t>
+          <t>435027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445700</t>
+          <t>445706</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>850335</t>
+          <t>849886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>867503</t>
+          <t>866773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28995</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38740</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280791</t>
+          <t>281621</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>299396</t>
+          <t>299707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>340640</t>
+          <t>340474</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>350994</t>
+          <t>351075</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>625042</t>
+          <t>628378</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>647503</t>
+          <t>648756</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>26854</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51015</t>
+          <t>51292</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>35683</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65021</t>
+          <t>63380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229412</t>
+          <t>231630</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244316</t>
+          <t>244631</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>337964</t>
+          <t>337687</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>362198</t>
+          <t>362125</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>573809</t>
+          <t>575450</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>602893</t>
+          <t>603147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>38818</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69570</t>
+          <t>69833</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83920</t>
+          <t>83422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>97841</t>
+          <t>98274</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142573</t>
+          <t>144032</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3357209</t>
+          <t>3356946</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3387687</t>
+          <t>3387961</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3471178</t>
+          <t>3471676</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3505287</t>
+          <t>3504696</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6839304</t>
+          <t>6837845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6884036</t>
+          <t>6883603</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2016</t>
+          <t>Población con diagnóstico de hipoacusia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,62 +3746,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5410</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5032</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413503</t>
+          <t>413731</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810186</t>
+          <t>809808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>554631</t>
+          <t>553860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562640</t>
+          <t>562643</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1145197</t>
+          <t>1145920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153163</t>
+          <t>1153140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664461</t>
+          <t>663721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652995</t>
+          <t>652230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1320360</t>
+          <t>1319566</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328669</t>
+          <t>1328663</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,82 +4755,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4382</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11189</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>11763</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>6437</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>20926</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4382</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1109</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10931</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>11763</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>6387</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>21325</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632008</t>
+          <t>631324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642841</t>
+          <t>642894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,82 +4868,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>644695</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>637888</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>647992</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1173</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1283362</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1274199</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1288688</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>644695</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>638146</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>647968</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1173</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1283362</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1273800</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1288738</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22202</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23144</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16698</t>
+          <t>16405</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41327</t>
+          <t>40258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455716</t>
+          <t>456028</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472364</t>
+          <t>472291</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>473705</t>
+          <t>472155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490292</t>
+          <t>489183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>933440</t>
+          <t>934509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>958069</t>
+          <t>958362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>34946</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>21402</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43471</t>
+          <t>43087</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>321497</t>
+          <t>322370</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332308</t>
+          <t>332272</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>343178</t>
+          <t>342816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>361252</t>
+          <t>360908</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>668621</t>
+          <t>669005</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>690885</t>
+          <t>690690</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32677</t>
+          <t>30822</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32395</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60793</t>
+          <t>57414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>224321</t>
+          <t>226176</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241871</t>
+          <t>242063</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>366704</t>
+          <t>366632</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386875</t>
+          <t>386267</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>596374</t>
+          <t>599753</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>624772</t>
+          <t>625282</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36995</t>
+          <t>36588</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65415</t>
+          <t>65709</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55721</t>
+          <t>57185</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90268</t>
+          <t>91946</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>100457</t>
+          <t>99982</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145200</t>
+          <t>145331</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3328935</t>
+          <t>3328641</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3357355</t>
+          <t>3357762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3454274</t>
+          <t>3452596</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3488821</t>
+          <t>3487357</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6793692</t>
+          <t>6793561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6838435</t>
+          <t>6838910</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2023</t>
+          <t>Población con diagnóstico de hipoacusia en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,97 +6690,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2499</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2499</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11768</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>14592</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2499</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>14310</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301432</t>
+          <t>300897</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698877</t>
+          <t>698595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12930</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416321</t>
+          <t>416395</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498574</t>
+          <t>497708</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508910</t>
+          <t>508810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920266</t>
+          <t>920335</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>931860</t>
+          <t>931571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>17619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518645</t>
+          <t>517784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531092</t>
+          <t>530990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537570</t>
+          <t>537965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541637</t>
+          <t>541634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1058186</t>
+          <t>1059347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1071865</t>
+          <t>1071891</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36855</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49413</t>
+          <t>48255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>850931</t>
+          <t>852911</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878655</t>
+          <t>879694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>690413</t>
+          <t>690378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>702921</t>
+          <t>702864</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1550439</t>
+          <t>1551597</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1577877</t>
+          <t>1579787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23812</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43798</t>
+          <t>44182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43100</t>
+          <t>43333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66686</t>
+          <t>68201</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>516439</t>
+          <t>516055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>536425</t>
+          <t>536101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>523146</t>
+          <t>523145</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>515147</t>
+          <t>514961</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>529198</t>
+          <t>529059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1037207</t>
+          <t>1035692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1060793</t>
+          <t>1060560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>543657</t>
+          <t>543656</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>543657</t>
+          <t>543656</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>543657</t>
+          <t>543656</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24411</t>
+          <t>24118</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>40936</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10910</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45074</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27808</t>
+          <t>30870</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79872</t>
+          <t>80020</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>326414</t>
+          <t>326511</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>343036</t>
+          <t>343329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>562934</t>
+          <t>562186</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>597098</t>
+          <t>598410</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>895583</t>
+          <t>895435</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>947647</t>
+          <t>944585</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47980</t>
+          <t>47531</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69302</t>
+          <t>67626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76078</t>
+          <t>76246</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98756</t>
+          <t>99347</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129389</t>
+          <t>130407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160835</t>
+          <t>160861</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>213457</t>
+          <t>215133</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>234779</t>
+          <t>235228</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326915</t>
+          <t>326324</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>349593</t>
+          <t>349425</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>547595</t>
+          <t>547569</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>579041</t>
+          <t>578023</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,59%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120677</t>
+          <t>118802</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>179778</t>
+          <t>179133</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132119</t>
+          <t>130509</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>182663</t>
+          <t>181385</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>273975</t>
+          <t>272030</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>350189</t>
+          <t>351359</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3277152</t>
+          <t>3277797</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3336253</t>
+          <t>3338128</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3473241</t>
+          <t>3474519</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3523785</t>
+          <t>3525395</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6762645</t>
+          <t>6761475</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6838859</t>
+          <t>6840804</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1426-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1426-Edad-trans_orig.xlsx
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12014</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18557</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>673400</t>
+          <t>673414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686155</t>
+          <t>686164</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>598241</t>
+          <t>599053</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609319</t>
+          <t>609309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1278785</t>
+          <t>1279141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294399</t>
+          <t>1294566</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670327</t>
+          <t>671090</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680055</t>
+          <t>680111</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>697975</t>
+          <t>697731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>708533</t>
+          <t>708521</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1373792</t>
+          <t>1374725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1386987</t>
+          <t>1386778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>17555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604204</t>
+          <t>603617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613589</t>
+          <t>613566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601123</t>
+          <t>600934</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612124</t>
+          <t>611279</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1209498</t>
+          <t>1211325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1223656</t>
+          <t>1223641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27343</t>
+          <t>25749</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>410283</t>
+          <t>410102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>423969</t>
+          <t>424143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>435027</t>
+          <t>434891</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445706</t>
+          <t>445612</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>849886</t>
+          <t>851480</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>866773</t>
+          <t>867731</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28165</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>36367</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281621</t>
+          <t>280663</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>299707</t>
+          <t>299555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>340474</t>
+          <t>340122</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>351075</t>
+          <t>351080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>628378</t>
+          <t>627415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>648756</t>
+          <t>647834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18221</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26854</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51292</t>
+          <t>51865</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35683</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>64149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>231630</t>
+          <t>230804</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244631</t>
+          <t>244636</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>337687</t>
+          <t>337114</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>362125</t>
+          <t>362422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>575450</t>
+          <t>574681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>603147</t>
+          <t>602588</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38818</t>
+          <t>38013</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69833</t>
+          <t>68462</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>50236</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83422</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>98281</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>144032</t>
+          <t>147293</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3356946</t>
+          <t>3358317</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3387961</t>
+          <t>3388766</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3471676</t>
+          <t>3471282</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3504696</t>
+          <t>3504862</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6837845</t>
+          <t>6834584</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6883603</t>
+          <t>6883596</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413731</t>
+          <t>415393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809808</t>
+          <t>810164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>553860</t>
+          <t>554663</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562643</t>
+          <t>562668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1145920</t>
+          <t>1145192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153140</t>
+          <t>1153144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663721</t>
+          <t>664510</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652230</t>
+          <t>652904</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660457</t>
+          <t>660463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1319566</t>
+          <t>1320344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328663</t>
+          <t>1328661</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631324</t>
+          <t>631294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642894</t>
+          <t>642930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>637888</t>
+          <t>638175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>647992</t>
+          <t>647982</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1274199</t>
+          <t>1274713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1288688</t>
+          <t>1288917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>22255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40258</t>
+          <t>39043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456028</t>
+          <t>455663</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472291</t>
+          <t>472292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472155</t>
+          <t>472807</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489183</t>
+          <t>489146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>934509</t>
+          <t>935724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>958362</t>
+          <t>958444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34946</t>
+          <t>36024</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21402</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>41473</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322370</t>
+          <t>323115</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332272</t>
+          <t>332321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342816</t>
+          <t>341738</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>360908</t>
+          <t>361021</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>669005</t>
+          <t>670619</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>690690</t>
+          <t>691553</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14935</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>34381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>33113</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57414</t>
+          <t>59218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226176</t>
+          <t>226592</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242063</t>
+          <t>242527</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>366632</t>
+          <t>365788</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386267</t>
+          <t>386667</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>599753</t>
+          <t>597949</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>625282</t>
+          <t>624054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36588</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65709</t>
+          <t>64386</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57185</t>
+          <t>55309</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91946</t>
+          <t>91540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99982</t>
+          <t>100489</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145331</t>
+          <t>148343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3328641</t>
+          <t>3329964</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3357762</t>
+          <t>3358014</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3452596</t>
+          <t>3453002</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3487357</t>
+          <t>3489233</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6793561</t>
+          <t>6790549</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6838910</t>
+          <t>6838403</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6833,27 +6833,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>310701</t>
+          <t>360196</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300897</t>
+          <t>348433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6868,27 +6868,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>710688</t>
+          <t>767989</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698595</t>
+          <t>756512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7063,22 +7063,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -7141,27 +7141,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>422276</t>
+          <t>475668</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416395</t>
+          <t>470598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7176,27 +7176,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>505238</t>
+          <t>494599</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497708</t>
+          <t>488763</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508810</t>
+          <t>498412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7211,32 +7211,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>927513</t>
+          <t>970267</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920335</t>
+          <t>962683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>931571</t>
+          <t>974535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7371,32 +7371,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7406,32 +7406,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,32 +7441,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>20185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -7484,32 +7484,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>526495</t>
+          <t>609878</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517784</t>
+          <t>601313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530990</t>
+          <t>614943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7519,32 +7519,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>540494</t>
+          <t>619528</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537965</t>
+          <t>615497</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541634</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7554,32 +7554,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1066989</t>
+          <t>1229406</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1059347</t>
+          <t>1220972</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1071891</t>
+          <t>1235454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535167</t>
+          <t>619669</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535167</t>
+          <t>619669</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535167</t>
+          <t>619669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076966</t>
+          <t>1241157</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076966</t>
+          <t>1241157</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076966</t>
+          <t>1241157</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21164</t>
+          <t>22194</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>35186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>15912</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21688</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>35832</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20065</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48255</t>
+          <t>52398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>866622</t>
+          <t>678423</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>852911</t>
+          <t>665431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879694</t>
+          <t>686072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>697398</t>
+          <t>720129</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>690378</t>
+          <t>712704</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>702864</t>
+          <t>725406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1564020</t>
+          <t>1398552</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1551597</t>
+          <t>1384260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1579787</t>
+          <t>1408065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712066</t>
+          <t>736041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712066</t>
+          <t>736041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712066</t>
+          <t>736041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599852</t>
+          <t>1436658</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599852</t>
+          <t>1436658</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599852</t>
+          <t>1436658</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32996</t>
+          <t>33759</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44182</t>
+          <t>45571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>23641</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14597</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28695</t>
+          <t>32404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>57400</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43333</t>
+          <t>46326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68201</t>
+          <t>71722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>527241</t>
+          <t>574600</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>516055</t>
+          <t>562788</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>536101</t>
+          <t>583702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>523145</t>
+          <t>582502</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>514961</t>
+          <t>573739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>529059</t>
+          <t>589348</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,32 +8240,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1050386</t>
+          <t>1157102</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1035692</t>
+          <t>1142780</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1060560</t>
+          <t>1168176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>543656</t>
+          <t>606143</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>543656</t>
+          <t>606143</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>543656</t>
+          <t>606143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1103893</t>
+          <t>1214502</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1103893</t>
+          <t>1214502</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1103893</t>
+          <t>1214502</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>34877</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24118</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40936</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>23531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45822</t>
+          <t>39564</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>59833</t>
+          <t>64986</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30870</t>
+          <t>53763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80020</t>
+          <t>77821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>335196</t>
+          <t>371334</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>326511</t>
+          <t>361383</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>343329</t>
+          <t>379875</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>580426</t>
+          <t>408673</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>562186</t>
+          <t>399218</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>598410</t>
+          <t>415251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>915622</t>
+          <t>780007</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>895435</t>
+          <t>767172</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>944585</t>
+          <t>791230</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608008</t>
+          <t>438782</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608008</t>
+          <t>438782</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608008</t>
+          <t>438782</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975455</t>
+          <t>844993</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975455</t>
+          <t>844993</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975455</t>
+          <t>844993</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>57782</t>
+          <t>62267</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47531</t>
+          <t>52329</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67626</t>
+          <t>74155</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>87569</t>
+          <t>94089</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76246</t>
+          <t>81626</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99347</t>
+          <t>106676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>145351</t>
+          <t>156356</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130407</t>
+          <t>139164</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160861</t>
+          <t>173710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>224977</t>
+          <t>247931</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>215133</t>
+          <t>236043</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>235228</t>
+          <t>257869</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>338102</t>
+          <t>369843</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326324</t>
+          <t>357256</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>349425</t>
+          <t>382306</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>563079</t>
+          <t>617774</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>547569</t>
+          <t>600420</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>578023</t>
+          <t>634966</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425671</t>
+          <t>463932</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425671</t>
+          <t>463932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425671</t>
+          <t>463932</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708430</t>
+          <t>774130</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708430</t>
+          <t>774130</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708430</t>
+          <t>774130</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>154136</t>
+          <t>164110</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118802</t>
+          <t>143078</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>179133</t>
+          <t>185982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>160400</t>
+          <t>174510</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130509</t>
+          <t>154437</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>181385</t>
+          <t>193746</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>314536</t>
+          <t>338620</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>272030</t>
+          <t>307362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>351359</t>
+          <t>366562</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3302794</t>
+          <t>3365628</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3277797</t>
+          <t>3343756</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3338128</t>
+          <t>3386660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3495504</t>
+          <t>3555471</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3474519</t>
+          <t>3536235</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3525395</t>
+          <t>3575544</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6798298</t>
+          <t>6921099</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6761475</t>
+          <t>6893157</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6840804</t>
+          <t>6952357</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456930</t>
+          <t>3529738</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456930</t>
+          <t>3529738</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456930</t>
+          <t>3529738</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3655904</t>
+          <t>3729981</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3655904</t>
+          <t>3729981</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3655904</t>
+          <t>3729981</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7112834</t>
+          <t>7259719</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7112834</t>
+          <t>7259719</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7112834</t>
+          <t>7259719</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
